--- a/artfynd/A 38437-2021 artfynd.xlsx
+++ b/artfynd/A 38437-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38437-2021 artfynd.xlsx
+++ b/artfynd/A 38437-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92156381</v>
+        <v>129462516</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klabböle energi, Vb</t>
+          <t>Färlavarpet, Färlavarpet, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751934.0415158583</v>
+        <v>752093</v>
       </c>
       <c r="R2" t="n">
-        <v>7088689.758482133</v>
+        <v>7088649</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-04-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-04-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Berit Nilsson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Berit Nilsson</t>
+          <t>Simon Mattsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112666513</v>
+        <v>92156381</v>
       </c>
       <c r="B3" t="n">
-        <v>102466</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,20 +800,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klabböle energicentrum, Vb</t>
+          <t>Klabböle energi, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751898</v>
+        <v>751934</v>
       </c>
       <c r="R3" t="n">
-        <v>7088715</v>
+        <v>7088690</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,12 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2020-04-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-11</t>
+          <t>2020-04-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,18 +859,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Berit Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Berit Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -901,12 +881,7 @@
         <v>112666509</v>
       </c>
       <c r="B4" t="n">
-        <v>102466</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,6 +972,103 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112666513</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Klabböle energicentrum, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>751898</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7088715</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
